--- a/docs/downloads/05/tbl_cooking_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/05/tbl_cooking_alaotra_ambatoharanana.xlsx
@@ -405,12 +405,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -440,12 +434,6 @@
         <is>
           <t>Gaz</t>
         </is>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.2</v>
       </c>
     </row>
     <row r="6">

--- a/docs/downloads/05/tbl_cooking_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/05/tbl_cooking_alaotra_ambatoharanana.xlsx
@@ -384,7 +384,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C2">
@@ -421,7 +421,7 @@
         <v>218</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -444,14 +444,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C6">
         <v>420</v>
       </c>
       <c r="D6">
-        <v>65.5</v>
+        <v>82.8</v>
       </c>
     </row>
   </sheetData>
